--- a/Data/canonical_files/international_climate_nature_governance.xlsx
+++ b/Data/canonical_files/international_climate_nature_governance.xlsx
@@ -1219,7 +1219,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>[POL-003] UK National Biodiversity Strategy and Action Plan (NBSAP) 2025; [ORG-004] Joint Nature Conservation Committee (JNCC); [POL-022] 30×30 Technical Working Group; [LEG-004] Environment Act 2021; JNCC UK Biodiversity Indicators; UN Convention on Biological Diversity (CBD) / Kunming-Montreal GBF</t>
+          <t>[POL-003] UK National Biodiversity Strategy and Action Plan (NBSAP) 2025; [ORG-004] Joint Nature Conservation Committee (JNCC); [POL-022] 30×30 Technical Working Group; [LEG-004] Environment Act 2021; JNCC UK Biodiversity Indicators; UN Convention on Biological Diversity (CBD) / Kunming-Montreal GBF; [POL-078] 30by30 on land in England; [POL-110] 30 by 30 in Scotland</t>
         </is>
       </c>
       <c r="Q8" s="2" t="n"/>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>[ORG-007] Office for Environmental Protection (OEP); [LEG-004] Environment Act 2021; [LEG-009] Environmental Principles Policy Statement (EPPS) 2023</t>
+          <t>[ORG-007] Office for Environmental Protection (OEP); [LEG-004] Environment Act 2021; [POL-111] Environmental Principles Policy Statement (EPPS)</t>
         </is>
       </c>
       <c r="Q23" s="3" t="n"/>
@@ -14741,7 +14741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="19" min="1" max="1"/>
@@ -14769,7 +14769,7 @@
         </is>
       </c>
       <c r="B2" s="15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="19">
@@ -14780,7 +14780,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -14928,6 +14928,50 @@
         </is>
       </c>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>Cowork (Claude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>v17</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>v17: INT-L-007 UK_Links gains [POL-078] 30by30 on land in England and [POL-110] 30 by 30 in Scotland, reciprocal to their new Intl_Links (UK governance v27).</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cowork (Claude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>v18</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>v18: INT-L-022 Aarhus UK_Links: LEG-009 (retired) repointed to [POL-111] — the EPPS moved from the UK Legislation sheet to Policies &amp; Activities in UK governance v29.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Cowork (Claude)</t>
         </is>
